--- a/artfynd/A 68593-2021 artfynd.xlsx
+++ b/artfynd/A 68593-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68593-2021 artfynd.xlsx
+++ b/artfynd/A 68593-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97363328</v>
+        <v>102282275</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524372.6427125565</v>
+        <v>524441</v>
       </c>
       <c r="R2" t="n">
-        <v>7027293.460081129</v>
+        <v>7027504</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,40 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97363326</v>
+        <v>102283350</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524155.6823135531</v>
+        <v>524236</v>
       </c>
       <c r="R3" t="n">
-        <v>7027232.600949201</v>
+        <v>7027759</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,31 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97363323</v>
+        <v>102284256</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524381.4148721916</v>
+        <v>524149</v>
       </c>
       <c r="R4" t="n">
-        <v>7027321.340257755</v>
+        <v>7027421</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,31 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102282243</v>
+        <v>102284257</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524458.7873695674</v>
+        <v>524130</v>
       </c>
       <c r="R5" t="n">
-        <v>7027601.396867688</v>
+        <v>7027438</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,19 +1034,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102284256</v>
+        <v>102284229</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524149.3180599832</v>
+        <v>524170</v>
       </c>
       <c r="R6" t="n">
-        <v>7027421.413921427</v>
+        <v>7027409</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,19 +1131,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,50 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102282261</v>
+        <v>102356319</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>524442.528268638</v>
+        <v>524444</v>
       </c>
       <c r="R7" t="n">
-        <v>7027554.173325189</v>
+        <v>7027520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,54 +1231,40 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102283343</v>
+        <v>102282232</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,37 +1272,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>524238.7851783687</v>
+        <v>524456</v>
       </c>
       <c r="R8" t="n">
-        <v>7027767.483355176</v>
+        <v>7027687</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,19 +1329,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,27 +1346,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102284217</v>
+        <v>102282233</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,37 +1369,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>524431.1649579767</v>
+        <v>524459</v>
       </c>
       <c r="R9" t="n">
-        <v>7027512.817987674</v>
+        <v>7027577</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,19 +1426,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,65 +1443,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102283337</v>
+        <v>102282234</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>524239.6596693537</v>
+        <v>524436</v>
       </c>
       <c r="R10" t="n">
-        <v>7027770.629745578</v>
+        <v>7027500</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,19 +1523,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,27 +1540,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102282260</v>
+        <v>102283339</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,37 +1563,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>524458.7873695674</v>
+        <v>524447</v>
       </c>
       <c r="R11" t="n">
-        <v>7027601.396867688</v>
+        <v>7027697</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,19 +1620,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,49 +1637,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102282259</v>
+        <v>102282260</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1852,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>524318.1163658509</v>
+        <v>524459</v>
       </c>
       <c r="R12" t="n">
-        <v>7027730.406896437</v>
+        <v>7027601</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,19 +1717,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,53 +1746,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102283338</v>
+        <v>102282261</v>
       </c>
       <c r="B13" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>524469.1249962556</v>
+        <v>524442</v>
       </c>
       <c r="R13" t="n">
-        <v>7027659.339926363</v>
+        <v>7027554</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,19 +1814,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,65 +1831,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102282240</v>
+        <v>102284242</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>524235.5314459488</v>
+        <v>524466</v>
       </c>
       <c r="R14" t="n">
-        <v>7027722.604479064</v>
+        <v>7027553</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,19 +1911,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,27 +1928,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102284229</v>
+        <v>102284243</v>
       </c>
       <c r="B15" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,21 +1951,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>524170.5271289091</v>
+        <v>524130</v>
       </c>
       <c r="R15" t="n">
-        <v>7027408.564748003</v>
+        <v>7027441</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,19 +2008,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,15 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102282246</v>
+        <v>97363324</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2276,21 +2048,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524458.9722432382</v>
+        <v>524340</v>
       </c>
       <c r="R16" t="n">
-        <v>7027577.175773125</v>
+        <v>7027120</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,22 +2102,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,65 +2122,64 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102284226</v>
+        <v>97363326</v>
       </c>
       <c r="B17" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524411.0436133575</v>
+        <v>524156</v>
       </c>
       <c r="R17" t="n">
-        <v>7027441.788937664</v>
+        <v>7027232</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,22 +2203,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,27 +2223,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102282245</v>
+        <v>102283334</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,37 +2250,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524445.0349822314</v>
+        <v>524449</v>
       </c>
       <c r="R18" t="n">
-        <v>7027578.863689709</v>
+        <v>7027553</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2557,19 +2307,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,65 +2324,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102282228</v>
+        <v>102284217</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524446.5192978382</v>
+        <v>524431</v>
       </c>
       <c r="R19" t="n">
-        <v>7027560.932309195</v>
+        <v>7027513</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2669,19 +2404,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,27 +2421,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102282242</v>
+        <v>102283345</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,37 +2444,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524445.5509289728</v>
+        <v>524467</v>
       </c>
       <c r="R20" t="n">
-        <v>7027687.867398089</v>
+        <v>7027636</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2781,19 +2501,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,27 +2518,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102282232</v>
+        <v>97363323</v>
       </c>
       <c r="B21" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,21 +2541,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2565,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524455.8878121354</v>
+        <v>524382</v>
       </c>
       <c r="R21" t="n">
-        <v>7027687.04917129</v>
+        <v>7027322</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,22 +2595,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,65 +2615,64 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102284242</v>
+        <v>97363328</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524465.4418067394</v>
+        <v>524373</v>
       </c>
       <c r="R22" t="n">
-        <v>7027553.451041463</v>
+        <v>7027293</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3002,22 +2696,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,69 +2712,73 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102282275</v>
+        <v>102284226</v>
       </c>
       <c r="B23" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524441.1148238805</v>
+        <v>524411</v>
       </c>
       <c r="R23" t="n">
-        <v>7027503.922336366</v>
+        <v>7027442</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3117,19 +2805,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,27 +2822,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102282241</v>
+        <v>102282240</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524319.5318262441</v>
+        <v>524235</v>
       </c>
       <c r="R24" t="n">
-        <v>7027721.446728785</v>
+        <v>7027722</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,19 +2902,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,44 +2924,39 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102282272</v>
+        <v>102282241</v>
       </c>
       <c r="B25" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3308,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524445.0349822314</v>
+        <v>524319</v>
       </c>
       <c r="R25" t="n">
-        <v>7027578.863689709</v>
+        <v>7027721</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,19 +2999,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,60 +3021,55 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102284230</v>
+        <v>102282242</v>
       </c>
       <c r="B26" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524350.0046796061</v>
+        <v>524446</v>
       </c>
       <c r="R26" t="n">
-        <v>7027435.044361277</v>
+        <v>7027688</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3453,19 +3096,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,27 +3113,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102282234</v>
+        <v>102282243</v>
       </c>
       <c r="B27" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,21 +3136,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3532,10 +3160,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524436.2048713302</v>
+        <v>524459</v>
       </c>
       <c r="R27" t="n">
-        <v>7027499.847698527</v>
+        <v>7027601</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,19 +3193,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,22 +3215,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102283345</v>
+        <v>102282244</v>
       </c>
       <c r="B28" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3620,37 +3233,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524467.5031167411</v>
+        <v>524453</v>
       </c>
       <c r="R28" t="n">
-        <v>7027636.451147064</v>
+        <v>7027597</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3677,19 +3290,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,27 +3307,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102282233</v>
+        <v>102282245</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,21 +3330,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3756,10 +3354,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524458.9722432382</v>
+        <v>524445</v>
       </c>
       <c r="R29" t="n">
-        <v>7027577.175773125</v>
+        <v>7027579</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,19 +3387,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,22 +3409,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102284366</v>
+        <v>102282246</v>
       </c>
       <c r="B30" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3864,17 +3447,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524465.4418067394</v>
+        <v>524459</v>
       </c>
       <c r="R30" t="n">
-        <v>7027553.451041463</v>
+        <v>7027577</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3901,60 +3484,39 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102283334</v>
+        <v>102282247</v>
       </c>
       <c r="B31" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,37 +3524,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>..., Jmt</t>
+          <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524448.3740729082</v>
+        <v>524429</v>
       </c>
       <c r="R31" t="n">
-        <v>7027553.320779968</v>
+        <v>7027540</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4019,19 +3581,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,49 +3598,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102282226</v>
+        <v>102282248</v>
       </c>
       <c r="B32" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +3645,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524445.0349822314</v>
+        <v>524436</v>
       </c>
       <c r="R32" t="n">
-        <v>7027578.863689709</v>
+        <v>7027501</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4131,19 +3678,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4163,22 +3700,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102282248</v>
+        <v>102283343</v>
       </c>
       <c r="B33" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,17 +3738,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524436.1946101668</v>
+        <v>524239</v>
       </c>
       <c r="R33" t="n">
-        <v>7027501.193352049</v>
+        <v>7027767</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4243,19 +3775,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,27 +3792,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102283339</v>
+        <v>102284366</v>
       </c>
       <c r="B34" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4298,21 +3815,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,10 +3839,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524446.8298864327</v>
+        <v>524466</v>
       </c>
       <c r="R34" t="n">
-        <v>7027696.848165426</v>
+        <v>7027553</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4355,19 +3872,14 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,6 +3888,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4387,22 +3900,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102282273</v>
+        <v>102282226</v>
       </c>
       <c r="B35" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4410,21 +3918,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4434,10 +3942,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524433.0676024972</v>
+        <v>524445</v>
       </c>
       <c r="R35" t="n">
-        <v>7027498.926622281</v>
+        <v>7027579</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,19 +3975,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4499,60 +3997,55 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102282247</v>
+        <v>102283337</v>
       </c>
       <c r="B36" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524429.6123190422</v>
+        <v>524240</v>
       </c>
       <c r="R36" t="n">
-        <v>7027539.720569692</v>
+        <v>7027770</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4579,19 +4072,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4606,65 +4089,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102282244</v>
+        <v>102283338</v>
       </c>
       <c r="B37" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Norbergsknulen, Jmt</t>
+          <t>..., Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524452.9793002887</v>
+        <v>524469</v>
       </c>
       <c r="R37" t="n">
-        <v>7027597.315469814</v>
+        <v>7027659</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4691,19 +4169,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4718,65 +4186,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>102356319</v>
+        <v>102282272</v>
       </c>
       <c r="B38" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Norbergsknulen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524443.6865986784</v>
+        <v>524445</v>
       </c>
       <c r="R38" t="n">
-        <v>7027520.090676283</v>
+        <v>7027579</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4806,43 +4266,420 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>102282273</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norbergsknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>524433</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7027499</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall, Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>102284241</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>524130</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7027441</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Maria Danvind</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>102284230</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>..., Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>524350</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7027435</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Maria Danvind, Johan Råghall, Benny Öwre, Eva Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>102282228</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norbergsknulen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>524446</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7027561</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-07-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Maria Danvind, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68593-2021 artfynd.xlsx
+++ b/artfynd/A 68593-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282275</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284257</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102356319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282232</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282233</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282234</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283339</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282260</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282261</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284242</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284243</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363324</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363326</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283334</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284217</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283345</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2628,6 +2728,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363323</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363328</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284226</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282240</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282241</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282242</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282243</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282244</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282245</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3510,6 +3655,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282246</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282247</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282248</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3801,6 +3961,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283343</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3904,6 +4069,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284366</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4001,6 +4171,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282226</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4098,6 +4273,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283337</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4195,6 +4375,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102283338</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4292,6 +4477,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282272</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4389,6 +4579,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282273</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4486,6 +4681,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284241</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4583,6 +4783,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284230</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4680,8 +4885,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102282228</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>